--- a/artfynd/A 21221-2023 artfynd.xlsx
+++ b/artfynd/A 21221-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21221-2023 artfynd.xlsx
+++ b/artfynd/A 21221-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3769892</v>
+        <v>2386618</v>
       </c>
       <c r="B2" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575733.406053046</v>
+        <v>575733</v>
       </c>
       <c r="R2" t="n">
-        <v>6523979.488041488</v>
+        <v>6523979</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4902772</v>
+        <v>97757129</v>
       </c>
       <c r="B3" t="n">
-        <v>101679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,14 +808,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkvik, 200 m SV om Blommeborg, Srm</t>
+          <t>Fridhem, 500 m O om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575733.406053046</v>
+        <v>575372</v>
       </c>
       <c r="R3" t="n">
-        <v>6523979.488041488</v>
+        <v>6524071</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1989-07-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1989-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>örtrik granskog</t>
+          <t>blandsumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97756923</v>
+        <v>97756613</v>
       </c>
       <c r="B4" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575651.1516895636</v>
+        <v>575651</v>
       </c>
       <c r="R4" t="n">
-        <v>6524022.903826484</v>
+        <v>6524023</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97756924</v>
+        <v>3769892</v>
       </c>
       <c r="B5" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,14 +1012,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fridhem, 500 m O om, Srm</t>
+          <t>Björkvik, 200 m SV om Blommeborg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575372.2971593362</v>
+        <v>575733</v>
       </c>
       <c r="R5" t="n">
-        <v>6524071.277480245</v>
+        <v>6523979</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1096,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-07-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-07-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
+          <t>örtrik granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97757129</v>
+        <v>97756923</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>221423</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fridhem, 500 m O om, Srm</t>
+          <t>Fridhem, 650 m O om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575372.2971593362</v>
+        <v>575651</v>
       </c>
       <c r="R6" t="n">
-        <v>6524071.277480245</v>
+        <v>6524023</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
+          <t>örtrik barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97756752</v>
+        <v>97756924</v>
       </c>
       <c r="B7" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>221423</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575372.2971593362</v>
+        <v>575372</v>
       </c>
       <c r="R7" t="n">
-        <v>6524071.277480245</v>
+        <v>6524071</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,19 +1253,9 @@
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97757081</v>
+        <v>4902772</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fridhem, 500 m O om, Srm</t>
+          <t>Björkvik, 200 m SV om Blommeborg, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575372.2971593362</v>
+        <v>575733</v>
       </c>
       <c r="R8" t="n">
-        <v>6524071.277480245</v>
+        <v>6523979</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1447,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-07-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1983-07-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1989-07-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,7 +1371,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>blandsumpskog</t>
+          <t>örtrik granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97756613</v>
+        <v>97757081</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,34 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fridhem, 650 m O om, Srm</t>
+          <t>Fridhem, 500 m O om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575651.1516895636</v>
+        <v>575372</v>
       </c>
       <c r="R9" t="n">
-        <v>6524022.903826484</v>
+        <v>6524071</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,21 +1457,11 @@
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1983-07-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1473,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>örtrik barrskog</t>
+          <t>blandsumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1608,6 +1488,108 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97756752</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fridhem, 500 m O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575372</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6524071</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>1983-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1983-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21221-2023 artfynd.xlsx
+++ b/artfynd/A 21221-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2386618</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97757129</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97756613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3769892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97756923</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97756924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4902772</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97757081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,8 +1635,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97756752</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>